--- a/5_simulation/outputs/tables/supplementary/S6_score_degradation_summary.xlsx
+++ b/5_simulation/outputs/tables/supplementary/S6_score_degradation_summary.xlsx
@@ -480,16 +480,16 @@
         <v>31.7333828856</v>
       </c>
       <c r="E2" t="n">
-        <v>7.38462484389</v>
+        <v>7.39106754083</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.340607908181</v>
+        <v>-0.340589997825</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.37082368112</v>
+        <v>-0.370699162063</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.310049534518</v>
+        <v>-0.31001545559</v>
       </c>
       <c r="I2" t="n">
         <v>10</v>
@@ -511,16 +511,16 @@
         <v>34.1360296398</v>
       </c>
       <c r="E3" t="n">
-        <v>7.40932973345</v>
+        <v>7.41576895674</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.315903018617</v>
+        <v>-0.315888581919</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.345626109409</v>
+        <v>-0.345500278542</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.284021854963</v>
+        <v>-0.283975286215</v>
       </c>
       <c r="I3" t="n">
         <v>10</v>
@@ -542,16 +542,16 @@
         <v>35.9663315852</v>
       </c>
       <c r="E4" t="n">
-        <v>7.43055619563</v>
+        <v>7.43699532255</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.294676556433</v>
+        <v>-0.294662216109</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.326483239987</v>
+        <v>-0.326345545732</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.261686607157</v>
+        <v>-0.26163397619</v>
       </c>
       <c r="I4" t="n">
         <v>10</v>
@@ -573,16 +573,16 @@
         <v>38.7111515246</v>
       </c>
       <c r="E5" t="n">
-        <v>7.46185817793</v>
+        <v>7.46829326739</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.263374574141</v>
+        <v>-0.263364271268</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.295076169371</v>
+        <v>-0.295118257416</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.231437374787</v>
+        <v>-0.231412650631</v>
       </c>
       <c r="I5" t="n">
         <v>10</v>
@@ -604,16 +604,16 @@
         <v>42.8409382115</v>
       </c>
       <c r="E6" t="n">
-        <v>7.51328223564</v>
+        <v>7.51970895784</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.211950516431</v>
+        <v>-0.211948580815</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.248058195159</v>
+        <v>-0.248039916232</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.177013286808</v>
+        <v>-0.177027975088</v>
       </c>
       <c r="I6" t="n">
         <v>10</v>
@@ -635,16 +635,16 @@
         <v>45.2919445892</v>
       </c>
       <c r="E7" t="n">
-        <v>7.54566715091</v>
+        <v>7.55208147922</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.179565601161</v>
+        <v>-0.17957605944</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.214914078507</v>
+        <v>-0.214896120257</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.144760578837</v>
+        <v>-0.144783139972</v>
       </c>
       <c r="I7" t="n">
         <v>10</v>
@@ -666,16 +666,16 @@
         <v>48.0038636</v>
       </c>
       <c r="E8" t="n">
-        <v>7.57885570804</v>
+        <v>7.58527473537</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.146377044033</v>
+        <v>-0.146382803287</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.181213484428</v>
+        <v>-0.18128261502</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.106247404767</v>
+        <v>-0.106181660035</v>
       </c>
       <c r="I8" t="n">
         <v>10</v>
@@ -697,16 +697,16 @@
         <v>50.8519720099</v>
       </c>
       <c r="E9" t="n">
-        <v>7.61471732195</v>
+        <v>7.62112885063</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.110515430122</v>
+        <v>-0.110528688021</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.149252290553</v>
+        <v>-0.14926196656</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.074265093516</v>
+        <v>-0.0742442052547</v>
       </c>
       <c r="I9" t="n">
         <v>10</v>
@@ -728,16 +728,16 @@
         <v>53.1783953268</v>
       </c>
       <c r="E10" t="n">
-        <v>7.64290315535</v>
+        <v>7.6493094345</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.0823295967193</v>
+        <v>-0.0823481041546</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.116565368396</v>
+        <v>-0.116580681335</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.0504817756877</v>
+        <v>-0.0504462200055</v>
       </c>
       <c r="I10" t="n">
         <v>10</v>
@@ -756,16 +756,16 @@
         <v>60.3169737542</v>
       </c>
       <c r="E11" t="n">
-        <v>7.73443186725</v>
+        <v>7.74080211122</v>
       </c>
       <c r="F11" t="n">
-        <v>0.00919911518178</v>
+        <v>0.00914457256199</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.0241109594582</v>
+        <v>-0.0241560761601</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0434755849917</v>
+        <v>0.0433138626619</v>
       </c>
       <c r="I11" t="n">
         <v>10</v>
